--- a/excel/clientes_finanzas.xlsx
+++ b/excel/clientes_finanzas.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$I$470</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$I$475</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -3285,6 +3285,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I475"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3327,7 +3328,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -3356,7 +3357,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -3385,7 +3386,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -3414,7 +3415,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>175</v>
       </c>
@@ -3443,7 +3444,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -3472,7 +3473,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -3501,7 +3502,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>61</v>
       </c>
@@ -3530,7 +3531,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -3559,7 +3560,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>185</v>
       </c>
@@ -3588,7 +3589,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>276</v>
       </c>
@@ -3617,7 +3618,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -3646,7 +3647,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
@@ -3675,7 +3676,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>81</v>
       </c>
@@ -3704,7 +3705,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>762</v>
       </c>
@@ -3733,7 +3734,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>418</v>
       </c>
@@ -3762,7 +3763,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>452</v>
       </c>
@@ -3791,7 +3792,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>47</v>
       </c>
@@ -3820,7 +3821,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>183</v>
       </c>
@@ -3849,7 +3850,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>181</v>
       </c>
@@ -3878,7 +3879,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>274</v>
       </c>
@@ -3907,7 +3908,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -3936,7 +3937,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>187</v>
       </c>
@@ -3965,7 +3966,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>32</v>
       </c>
@@ -3994,7 +3995,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>350</v>
       </c>
@@ -4023,7 +4024,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>167</v>
       </c>
@@ -4052,7 +4053,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>207</v>
       </c>
@@ -4081,7 +4082,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>219</v>
       </c>
@@ -4110,7 +4111,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>262</v>
       </c>
@@ -4139,7 +4140,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>199</v>
       </c>
@@ -4168,7 +4169,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>49</v>
       </c>
@@ -4197,7 +4198,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>191</v>
       </c>
@@ -4226,7 +4227,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>223</v>
       </c>
@@ -4255,7 +4256,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>195</v>
       </c>
@@ -4284,7 +4285,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>907</v>
       </c>
@@ -4313,7 +4314,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>217</v>
       </c>
@@ -4342,7 +4343,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>304</v>
       </c>
@@ -4371,7 +4372,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>147</v>
       </c>
@@ -4400,7 +4401,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>221</v>
       </c>
@@ -4429,7 +4430,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>197</v>
       </c>
@@ -4458,7 +4459,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>26</v>
       </c>
@@ -4487,7 +4488,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>193</v>
       </c>
@@ -4516,7 +4517,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>252</v>
       </c>
@@ -4545,7 +4546,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>366</v>
       </c>
@@ -4574,7 +4575,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>65</v>
       </c>
@@ -4603,7 +4604,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>242</v>
       </c>
@@ -4632,7 +4633,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>77</v>
       </c>
@@ -4661,7 +4662,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>619</v>
       </c>
@@ -4690,7 +4691,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>211</v>
       </c>
@@ -4748,7 +4749,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>37</v>
       </c>
@@ -4777,7 +4778,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>59</v>
       </c>
@@ -4806,7 +4807,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>30</v>
       </c>
@@ -4835,7 +4836,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>428</v>
       </c>
@@ -4864,7 +4865,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>225</v>
       </c>
@@ -4893,7 +4894,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>310</v>
       </c>
@@ -4922,7 +4923,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>280</v>
       </c>
@@ -4951,7 +4952,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>240</v>
       </c>
@@ -4980,7 +4981,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>256</v>
       </c>
@@ -5009,7 +5010,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>63</v>
       </c>
@@ -5038,7 +5039,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>446</v>
       </c>
@@ -5067,7 +5068,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>236</v>
       </c>
@@ -5096,7 +5097,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>213</v>
       </c>
@@ -5125,7 +5126,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>316</v>
       </c>
@@ -5154,7 +5155,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>177</v>
       </c>
@@ -5183,7 +5184,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>258</v>
       </c>
@@ -5212,7 +5213,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>432</v>
       </c>
@@ -5241,7 +5242,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>20</v>
       </c>
@@ -5270,7 +5271,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>960</v>
       </c>
@@ -5299,7 +5300,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>268</v>
       </c>
@@ -5328,7 +5329,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>232</v>
       </c>
@@ -5357,7 +5358,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>306</v>
       </c>
@@ -5386,7 +5387,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>314</v>
       </c>
@@ -5415,7 +5416,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>209</v>
       </c>
@@ -5444,7 +5445,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>85</v>
       </c>
@@ -5473,7 +5474,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>282</v>
       </c>
@@ -5502,7 +5503,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>41</v>
       </c>
@@ -5531,7 +5532,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>230</v>
       </c>
@@ -5560,7 +5561,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>79</v>
       </c>
@@ -5589,7 +5590,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>201</v>
       </c>
@@ -5618,7 +5619,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>324</v>
       </c>
@@ -5647,7 +5648,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>117</v>
       </c>
@@ -5676,7 +5677,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>205</v>
       </c>
@@ -5705,7 +5706,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>358</v>
       </c>
@@ -5734,7 +5735,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>71</v>
       </c>
@@ -5763,7 +5764,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>322</v>
       </c>
@@ -5792,7 +5793,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>228</v>
       </c>
@@ -5821,7 +5822,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>942</v>
       </c>
@@ -5850,7 +5851,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>266</v>
       </c>
@@ -5879,7 +5880,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>91</v>
       </c>
@@ -5908,7 +5909,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>368</v>
       </c>
@@ -5937,7 +5938,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>344</v>
       </c>
@@ -5966,7 +5967,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>312</v>
       </c>
@@ -5995,7 +5996,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>246</v>
       </c>
@@ -6024,7 +6025,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>53</v>
       </c>
@@ -6053,7 +6054,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>189</v>
       </c>
@@ -6082,7 +6083,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>226</v>
       </c>
@@ -6111,7 +6112,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>286</v>
       </c>
@@ -6140,7 +6141,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>238</v>
       </c>
@@ -6169,7 +6170,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>298</v>
       </c>
@@ -6198,7 +6199,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>278</v>
       </c>
@@ -6227,7 +6228,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>109</v>
       </c>
@@ -6256,7 +6257,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>448</v>
       </c>
@@ -6285,7 +6286,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>444</v>
       </c>
@@ -6314,7 +6315,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>250</v>
       </c>
@@ -6343,7 +6344,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>55</v>
       </c>
@@ -6372,7 +6373,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>364</v>
       </c>
@@ -6401,7 +6402,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>73</v>
       </c>
@@ -6430,7 +6431,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>422</v>
       </c>
@@ -6459,7 +6460,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>51</v>
       </c>
@@ -6488,7 +6489,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>260</v>
       </c>
@@ -6517,7 +6518,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>270</v>
       </c>
@@ -6546,7 +6547,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>482</v>
       </c>
@@ -6575,7 +6576,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>909</v>
       </c>
@@ -6604,7 +6605,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>234</v>
       </c>
@@ -6633,7 +6634,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>928</v>
       </c>
@@ -6662,7 +6663,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>348</v>
       </c>
@@ -6691,7 +6692,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>45</v>
       </c>
@@ -6720,7 +6721,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>292</v>
       </c>
@@ -6749,7 +6750,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>637</v>
       </c>
@@ -6778,7 +6779,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>119</v>
       </c>
@@ -6807,7 +6808,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>320</v>
       </c>
@@ -6836,7 +6837,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>450</v>
       </c>
@@ -6865,7 +6866,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>597</v>
       </c>
@@ -6894,7 +6895,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>394</v>
       </c>
@@ -6923,7 +6924,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>95</v>
       </c>
@@ -6952,7 +6953,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>426</v>
       </c>
@@ -6981,7 +6982,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>414</v>
       </c>
@@ -7010,7 +7011,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>913</v>
       </c>
@@ -7039,7 +7040,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>760</v>
       </c>
@@ -7068,7 +7069,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>378</v>
       </c>
@@ -7097,7 +7098,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>89</v>
       </c>
@@ -7126,7 +7127,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>702</v>
       </c>
@@ -7155,7 +7156,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>67</v>
       </c>
@@ -7184,7 +7185,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>911</v>
       </c>
@@ -7213,7 +7214,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>352</v>
       </c>
@@ -7242,7 +7243,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>215</v>
       </c>
@@ -7271,7 +7272,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>342</v>
       </c>
@@ -7300,7 +7301,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>581</v>
       </c>
@@ -7329,7 +7330,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>105</v>
       </c>
@@ -7358,7 +7359,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>69</v>
       </c>
@@ -7387,7 +7388,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>75</v>
       </c>
@@ -7416,7 +7417,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>392</v>
       </c>
@@ -7445,7 +7446,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>346</v>
       </c>
@@ -7474,7 +7475,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>386</v>
       </c>
@@ -7503,7 +7504,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>629</v>
       </c>
@@ -7532,7 +7533,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>284</v>
       </c>
@@ -7561,7 +7562,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>502</v>
       </c>
@@ -7590,7 +7591,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>408</v>
       </c>
@@ -7619,7 +7620,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>107</v>
       </c>
@@ -7648,7 +7649,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>340</v>
       </c>
@@ -7677,7 +7678,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>157</v>
       </c>
@@ -7706,7 +7707,7 @@
         <v>46272</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>244</v>
       </c>
@@ -7735,7 +7736,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>402</v>
       </c>
@@ -7764,7 +7765,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>420</v>
       </c>
@@ -7793,7 +7794,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>468</v>
       </c>
@@ -7822,7 +7823,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>101</v>
       </c>
@@ -7851,7 +7852,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>374</v>
       </c>
@@ -7880,7 +7881,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>748</v>
       </c>
@@ -7909,7 +7910,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>551</v>
       </c>
@@ -7938,7 +7939,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>498</v>
       </c>
@@ -7967,7 +7968,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>494</v>
       </c>
@@ -7996,7 +7997,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>103</v>
       </c>
@@ -8025,7 +8026,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>294</v>
       </c>
@@ -8054,7 +8055,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>522</v>
       </c>
@@ -8083,7 +8084,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>362</v>
       </c>
@@ -8112,7 +8113,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>698</v>
       </c>
@@ -8141,7 +8142,7 @@
         <v>46139</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>962</v>
       </c>
@@ -8170,7 +8171,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>434</v>
       </c>
@@ -8199,7 +8200,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>376</v>
       </c>
@@ -8228,7 +8229,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>438</v>
       </c>
@@ -8257,7 +8258,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>440</v>
       </c>
@@ -8286,7 +8287,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>512</v>
       </c>
@@ -8315,7 +8316,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>203</v>
       </c>
@@ -8344,7 +8345,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>43</v>
       </c>
@@ -8373,7 +8374,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>97</v>
       </c>
@@ -8402,7 +8403,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>121</v>
       </c>
@@ -8431,7 +8432,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>506</v>
       </c>
@@ -8460,7 +8461,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>328</v>
       </c>
@@ -8489,7 +8490,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>406</v>
       </c>
@@ -8518,7 +8519,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>424</v>
       </c>
@@ -8547,7 +8548,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>360</v>
       </c>
@@ -8576,7 +8577,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>388</v>
       </c>
@@ -8605,7 +8606,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>611</v>
       </c>
@@ -8634,7 +8635,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>398</v>
       </c>
@@ -8663,7 +8664,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>458</v>
       </c>
@@ -8692,7 +8693,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>647</v>
       </c>
@@ -8721,7 +8722,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>750</v>
       </c>
@@ -8750,7 +8751,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>330</v>
       </c>
@@ -8779,7 +8780,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>83</v>
       </c>
@@ -8808,7 +8809,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>695</v>
       </c>
@@ -8837,7 +8838,7 @@
         <v>46261</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>534</v>
       </c>
@@ -8866,7 +8867,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>390</v>
       </c>
@@ -8895,7 +8896,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>93</v>
       </c>
@@ -8924,7 +8925,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>354</v>
       </c>
@@ -8953,7 +8954,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>442</v>
       </c>
@@ -8982,7 +8983,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>708</v>
       </c>
@@ -9011,7 +9012,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>412</v>
       </c>
@@ -9040,7 +9041,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>508</v>
       </c>
@@ -9069,7 +9070,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>679</v>
       </c>
@@ -9098,7 +9099,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>476</v>
       </c>
@@ -9127,7 +9128,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>734</v>
       </c>
@@ -9156,7 +9157,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>480</v>
       </c>
@@ -9185,7 +9186,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>609</v>
       </c>
@@ -9214,7 +9215,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>125</v>
       </c>
@@ -9243,7 +9244,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>99</v>
       </c>
@@ -9272,7 +9273,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>57</v>
       </c>
@@ -9301,7 +9302,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>504</v>
       </c>
@@ -9330,7 +9331,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>264</v>
       </c>
@@ -9359,7 +9360,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>410</v>
       </c>
@@ -9388,7 +9389,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>308</v>
       </c>
@@ -9417,7 +9418,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>575</v>
       </c>
@@ -9446,7 +9447,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>462</v>
       </c>
@@ -9475,7 +9476,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>651</v>
       </c>
@@ -9504,7 +9505,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>631</v>
       </c>
@@ -9533,7 +9534,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>958</v>
       </c>
@@ -9562,7 +9563,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>436</v>
       </c>
@@ -9591,7 +9592,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>155</v>
       </c>
@@ -9620,7 +9621,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>627</v>
       </c>
@@ -9649,7 +9650,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>736</v>
       </c>
@@ -9678,7 +9679,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>296</v>
       </c>
@@ -9707,7 +9708,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>649</v>
       </c>
@@ -9736,7 +9737,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>769</v>
       </c>
@@ -9765,7 +9766,7 @@
         <v>46119</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>653</v>
       </c>
@@ -9794,7 +9795,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>516</v>
       </c>
@@ -9823,7 +9824,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>746</v>
       </c>
@@ -9852,7 +9853,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>486</v>
       </c>
@@ -9881,7 +9882,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>526</v>
       </c>
@@ -9910,7 +9911,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>466</v>
       </c>
@@ -9939,7 +9940,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>567</v>
       </c>
@@ -9968,7 +9969,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>139</v>
       </c>
@@ -9997,7 +9998,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>520</v>
       </c>
@@ -10026,7 +10027,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>115</v>
       </c>
@@ -10055,7 +10056,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>671</v>
       </c>
@@ -10084,7 +10085,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>541</v>
       </c>
@@ -10113,7 +10114,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>948</v>
       </c>
@@ -10142,7 +10143,7 @@
         <v>46265</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>623</v>
       </c>
@@ -10171,7 +10172,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>613</v>
       </c>
@@ -10200,7 +10201,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>336</v>
       </c>
@@ -10229,7 +10230,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>537</v>
       </c>
@@ -10258,7 +10259,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>754</v>
       </c>
@@ -10287,7 +10288,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>490</v>
       </c>
@@ -10316,7 +10317,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>288</v>
       </c>
@@ -10345,7 +10346,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>524</v>
       </c>
@@ -10374,7 +10375,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>681</v>
       </c>
@@ -10403,7 +10404,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>488</v>
       </c>
@@ -10432,7 +10433,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>356</v>
       </c>
@@ -10461,7 +10462,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>530</v>
       </c>
@@ -10490,7 +10491,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>496</v>
       </c>
@@ -10519,7 +10520,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>518</v>
       </c>
@@ -10548,7 +10549,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>889</v>
       </c>
@@ -10577,7 +10578,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>595</v>
       </c>
@@ -10606,7 +10607,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>382</v>
       </c>
@@ -10635,7 +10636,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>478</v>
       </c>
@@ -10664,7 +10665,7 @@
         <v>46133</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>532</v>
       </c>
@@ -10693,7 +10694,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>528</v>
       </c>
@@ -10722,7 +10723,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>742</v>
       </c>
@@ -10751,7 +10752,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>254</v>
       </c>
@@ -10780,7 +10781,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>952</v>
       </c>
@@ -10809,7 +10810,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>474</v>
       </c>
@@ -10838,7 +10839,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>370</v>
       </c>
@@ -10867,7 +10868,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>87</v>
       </c>
@@ -10896,7 +10897,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>561</v>
       </c>
@@ -10925,7 +10926,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>543</v>
       </c>
@@ -10954,7 +10955,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>641</v>
       </c>
@@ -10983,7 +10984,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>728</v>
       </c>
@@ -11012,7 +11013,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>571</v>
       </c>
@@ -11041,7 +11042,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>661</v>
       </c>
@@ -11070,7 +11071,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>689</v>
       </c>
@@ -11099,7 +11100,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>607</v>
       </c>
@@ -11128,7 +11129,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>535</v>
       </c>
@@ -11157,7 +11158,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>615</v>
       </c>
@@ -11186,7 +11187,7 @@
         <v>46261</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>617</v>
       </c>
@@ -11215,7 +11216,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>123</v>
       </c>
@@ -11244,7 +11245,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>454</v>
       </c>
@@ -11273,7 +11274,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>372</v>
       </c>
@@ -11302,7 +11303,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>601</v>
       </c>
@@ -11331,7 +11332,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>384</v>
       </c>
@@ -11360,7 +11361,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>133</v>
       </c>
@@ -11389,7 +11390,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>380</v>
       </c>
@@ -11418,7 +11419,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>767</v>
       </c>
@@ -11447,7 +11448,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>35</v>
       </c>
@@ -11476,7 +11477,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>338</v>
       </c>
@@ -11505,7 +11506,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>589</v>
       </c>
@@ -11534,7 +11535,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>673</v>
       </c>
@@ -11563,7 +11564,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>936</v>
       </c>
@@ -11592,7 +11593,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>655</v>
       </c>
@@ -11621,7 +11622,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>510</v>
       </c>
@@ -11650,7 +11651,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>137</v>
       </c>
@@ -11679,7 +11680,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>16</v>
       </c>
@@ -11708,7 +11709,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>563</v>
       </c>
@@ -11737,7 +11738,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>539</v>
       </c>
@@ -11766,7 +11767,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>127</v>
       </c>
@@ -11795,7 +11796,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>675</v>
       </c>
@@ -11824,7 +11825,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>667</v>
       </c>
@@ -11853,7 +11854,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>740</v>
       </c>
@@ -11882,7 +11883,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>470</v>
       </c>
@@ -11911,7 +11912,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>143</v>
       </c>
@@ -11940,7 +11941,7 @@
         <v>46281</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>39</v>
       </c>
@@ -11969,7 +11970,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>724</v>
       </c>
@@ -11998,7 +11999,7 @@
         <v>46246</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>555</v>
       </c>
@@ -12027,7 +12028,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>492</v>
       </c>
@@ -12056,7 +12057,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>557</v>
       </c>
@@ -12085,7 +12086,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>573</v>
       </c>
@@ -12114,7 +12115,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>621</v>
       </c>
@@ -12143,7 +12144,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>677</v>
       </c>
@@ -12172,7 +12173,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>605</v>
       </c>
@@ -12201,7 +12202,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>153</v>
       </c>
@@ -12230,7 +12231,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>113</v>
       </c>
@@ -12259,7 +12260,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>145</v>
       </c>
@@ -12288,7 +12289,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>716</v>
       </c>
@@ -12317,7 +12318,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>826</v>
       </c>
@@ -12346,7 +12347,7 @@
         <v>46240</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>129</v>
       </c>
@@ -12375,7 +12376,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>776</v>
       </c>
@@ -12404,7 +12405,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>956</v>
       </c>
@@ -12433,7 +12434,7 @@
         <v>46284</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>500</v>
       </c>
@@ -12462,7 +12463,7 @@
         <v>46133</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>165</v>
       </c>
@@ -12491,7 +12492,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>625</v>
       </c>
@@ -12520,7 +12521,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>396</v>
       </c>
@@ -12549,7 +12550,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>645</v>
       </c>
@@ -12578,7 +12579,7 @@
         <v>46084</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>643</v>
       </c>
@@ -12607,7 +12608,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>599</v>
       </c>
@@ -12636,7 +12637,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>553</v>
       </c>
@@ -12665,7 +12666,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>744</v>
       </c>
@@ -12694,7 +12695,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>484</v>
       </c>
@@ -12723,7 +12724,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>659</v>
       </c>
@@ -12752,7 +12753,7 @@
         <v>46255</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>593</v>
       </c>
@@ -12781,7 +12782,7 @@
         <v>46272</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>788</v>
       </c>
@@ -12810,7 +12811,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>923</v>
       </c>
@@ -12839,7 +12840,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>633</v>
       </c>
@@ -12868,7 +12869,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>932</v>
       </c>
@@ -12897,7 +12898,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>786</v>
       </c>
@@ -12926,7 +12927,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>163</v>
       </c>
@@ -12955,7 +12956,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>756</v>
       </c>
@@ -12984,7 +12985,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>718</v>
       </c>
@@ -13013,7 +13014,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>685</v>
       </c>
@@ -13042,7 +13043,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>430</v>
       </c>
@@ -13071,7 +13072,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>765</v>
       </c>
@@ -13100,7 +13101,7 @@
         <v>46200</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>665</v>
       </c>
@@ -13129,7 +13130,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>149</v>
       </c>
@@ -13158,7 +13159,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>565</v>
       </c>
@@ -13187,7 +13188,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>790</v>
       </c>
@@ -13216,7 +13217,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>712</v>
       </c>
@@ -13245,7 +13246,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>111</v>
       </c>
@@ -13274,7 +13275,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>577</v>
       </c>
@@ -13303,7 +13304,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>579</v>
       </c>
@@ -13332,7 +13333,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>472</v>
       </c>
@@ -13361,7 +13362,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>778</v>
       </c>
@@ -13390,7 +13391,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>930</v>
       </c>
@@ -13419,7 +13420,7 @@
         <v>46225</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>704</v>
       </c>
@@ -13448,7 +13449,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>549</v>
       </c>
@@ -13477,7 +13478,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>954</v>
       </c>
@@ -13506,7 +13507,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>326</v>
       </c>
@@ -13535,7 +13536,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>683</v>
       </c>
@@ -13564,7 +13565,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>569</v>
       </c>
@@ -13593,7 +13594,7 @@
         <v>46197</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>585</v>
       </c>
@@ -13622,7 +13623,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>460</v>
       </c>
@@ -13651,7 +13652,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>657</v>
       </c>
@@ -13680,7 +13681,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>726</v>
       </c>
@@ -13709,7 +13710,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>738</v>
       </c>
@@ -13738,7 +13739,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>940</v>
       </c>
@@ -13767,7 +13768,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>710</v>
       </c>
@@ -13796,7 +13797,7 @@
         <v>46147</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>559</v>
       </c>
@@ -13825,7 +13826,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>714</v>
       </c>
@@ -13854,7 +13855,7 @@
         <v>46270</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>635</v>
       </c>
@@ -13883,7 +13884,7 @@
         <v>46140</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>639</v>
       </c>
@@ -13912,7 +13913,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>758</v>
       </c>
@@ -13941,7 +13942,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>591</v>
       </c>
@@ -13970,7 +13971,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>669</v>
       </c>
@@ -13999,7 +14000,7 @@
         <v>46255</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>300</v>
       </c>
@@ -14028,7 +14029,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>290</v>
       </c>
@@ -14057,7 +14058,7 @@
         <v>46273</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>603</v>
       </c>
@@ -14086,7 +14087,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>332</v>
       </c>
@@ -14115,7 +14116,7 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>950</v>
       </c>
@@ -14144,7 +14145,7 @@
         <v>46265</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>587</v>
       </c>
@@ -14173,7 +14174,7 @@
         <v>46190</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>840</v>
       </c>
@@ -14202,7 +14203,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>946</v>
       </c>
@@ -14231,7 +14232,7 @@
         <v>46272</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>871</v>
       </c>
@@ -14260,7 +14261,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>855</v>
       </c>
@@ -14289,7 +14290,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>663</v>
       </c>
@@ -14318,7 +14319,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>893</v>
       </c>
@@ -14347,7 +14348,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>897</v>
       </c>
@@ -14376,7 +14377,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>891</v>
       </c>
@@ -14405,7 +14406,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>794</v>
       </c>
@@ -14434,7 +14435,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>885</v>
       </c>
@@ -14463,7 +14464,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>797</v>
       </c>
@@ -14492,7 +14493,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>774</v>
       </c>
@@ -14521,7 +14522,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>869</v>
       </c>
@@ -14550,7 +14551,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>815</v>
       </c>
@@ -14579,7 +14580,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>792</v>
       </c>
@@ -14608,7 +14609,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>865</v>
       </c>
@@ -14637,7 +14638,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>883</v>
       </c>
@@ -14666,7 +14667,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>899</v>
       </c>
@@ -14695,7 +14696,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>861</v>
       </c>
@@ -14724,7 +14725,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>822</v>
       </c>
@@ -14753,7 +14754,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>881</v>
       </c>
@@ -14782,7 +14783,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>895</v>
       </c>
@@ -14811,7 +14812,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>873</v>
       </c>
@@ -14840,7 +14841,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>179</v>
       </c>
@@ -14869,7 +14870,7 @@
         <v>46280</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>857</v>
       </c>
@@ -14898,7 +14899,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>863</v>
       </c>
@@ -14927,7 +14928,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>800</v>
       </c>
@@ -14956,7 +14957,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>813</v>
       </c>
@@ -14985,7 +14986,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>847</v>
       </c>
@@ -15014,7 +15015,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>838</v>
       </c>
@@ -15043,7 +15044,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>879</v>
       </c>
@@ -15072,7 +15073,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>819</v>
       </c>
@@ -15101,7 +15102,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>302</v>
       </c>
@@ -15130,7 +15131,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>805</v>
       </c>
@@ -15159,7 +15160,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>901</v>
       </c>
@@ -15188,7 +15189,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>842</v>
       </c>
@@ -15217,7 +15218,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>877</v>
       </c>
@@ -15246,7 +15247,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>832</v>
       </c>
@@ -15275,7 +15276,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>824</v>
       </c>
@@ -15304,7 +15305,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>867</v>
       </c>
@@ -15333,7 +15334,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>817</v>
       </c>
@@ -15362,7 +15363,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>784</v>
       </c>
@@ -15391,7 +15392,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>830</v>
       </c>
@@ -15420,7 +15421,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>807</v>
       </c>
@@ -15449,7 +15450,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>811</v>
       </c>
@@ -15478,7 +15479,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>404</v>
       </c>
@@ -15507,7 +15508,7 @@
         <v>46249</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>849</v>
       </c>
@@ -15536,7 +15537,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>851</v>
       </c>
@@ -15565,7 +15566,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>828</v>
       </c>
@@ -15594,7 +15595,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>802</v>
       </c>
@@ -15623,7 +15624,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>836</v>
       </c>
@@ -15652,7 +15653,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>853</v>
       </c>
@@ -15681,7 +15682,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>834</v>
       </c>
@@ -15710,7 +15711,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>845</v>
       </c>
@@ -15739,7 +15740,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>875</v>
       </c>
@@ -15768,7 +15769,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>809</v>
       </c>
@@ -15797,7 +15798,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>318</v>
       </c>
@@ -15826,7 +15827,7 @@
         <v>46098</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>859</v>
       </c>
@@ -15855,7 +15856,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>887</v>
       </c>
@@ -15884,7 +15885,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>141</v>
       </c>
@@ -15913,7 +15914,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>700</v>
       </c>
@@ -15942,7 +15943,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>780</v>
       </c>
@@ -15971,7 +15972,7 @@
         <v>46157</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>706</v>
       </c>
@@ -16000,7 +16001,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>151</v>
       </c>
@@ -16029,7 +16030,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>545</v>
       </c>
@@ -16058,7 +16059,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>697</v>
       </c>
@@ -16087,7 +16088,7 @@
         <v>46147</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>159</v>
       </c>
@@ -16116,7 +16117,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>456</v>
       </c>
@@ -16145,7 +16146,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>583</v>
       </c>
@@ -16174,7 +16175,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>944</v>
       </c>
@@ -16203,7 +16204,7 @@
         <v>46259</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>334</v>
       </c>
@@ -16232,7 +16233,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>730</v>
       </c>
@@ -16261,7 +16262,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>131</v>
       </c>
@@ -16290,7 +16291,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>763</v>
       </c>
@@ -16319,7 +16320,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>691</v>
       </c>
@@ -16348,7 +16349,7 @@
         <v>46153</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>693</v>
       </c>
@@ -16377,7 +16378,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>782</v>
       </c>
@@ -16406,7 +16407,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>272</v>
       </c>
@@ -16435,7 +16436,7 @@
         <v>46267</v>
       </c>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>722</v>
       </c>
@@ -16464,7 +16465,7 @@
         <v>46289</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>938</v>
       </c>
@@ -16493,7 +16494,7 @@
         <v>46255</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>732</v>
       </c>
@@ -16522,7 +16523,7 @@
         <v>46226</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>547</v>
       </c>
@@ -16551,7 +16552,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>416</v>
       </c>
@@ -16580,7 +16581,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>687</v>
       </c>
@@ -16609,7 +16610,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>464</v>
       </c>
@@ -16638,7 +16639,7 @@
         <v>46209</v>
       </c>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>720</v>
       </c>
@@ -16667,7 +16668,7 @@
         <v>46228</v>
       </c>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>934</v>
       </c>
@@ -16696,7 +16697,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>921</v>
       </c>
@@ -16725,7 +16726,7 @@
         <v>46220</v>
       </c>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>919</v>
       </c>
@@ -16754,7 +16755,7 @@
         <v>46238</v>
       </c>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>135</v>
       </c>
@@ -16783,7 +16784,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>915</v>
       </c>
@@ -16812,7 +16813,7 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>964</v>
       </c>
@@ -16841,7 +16842,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>903</v>
       </c>
@@ -16870,7 +16871,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>752</v>
       </c>
@@ -16899,7 +16900,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>514</v>
       </c>
@@ -16928,7 +16929,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>925</v>
       </c>
@@ -16957,7 +16958,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>248</v>
       </c>
@@ -16986,7 +16987,7 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>905</v>
       </c>
@@ -17015,7 +17016,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>917</v>
       </c>
@@ -17044,7 +17045,7 @@
         <v>46275</v>
       </c>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>161</v>
       </c>
@@ -17074,7 +17075,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I470"/>
+  <autoFilter ref="A1:I475">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="R.R FERRETERIA"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/excel/clientes_finanzas.xlsx
+++ b/excel/clientes_finanzas.xlsx
@@ -2750,9 +2750,6 @@
     <t>FERRETERIA GUATEMALA</t>
   </si>
   <si>
-    <t>CORRALON DE MATERIAL</t>
-  </si>
-  <si>
     <t>90714</t>
   </si>
   <si>
@@ -2895,6 +2892,9 @@
   </si>
   <si>
     <t>FERRETERIA RyV</t>
+  </si>
+  <si>
+    <t>COR. DE MATERIALES CABOT</t>
   </si>
 </sst>
 </file>
@@ -4517,10 +4517,10 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>939</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>940</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>34</v>
@@ -5648,10 +5648,10 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>921</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>922</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>5</v>
@@ -5912,7 +5912,7 @@
         <v>221</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>907</v>
+        <v>955</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>13</v>
@@ -6576,10 +6576,10 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>952</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>953</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>13</v>
@@ -6634,10 +6634,10 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>908</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>909</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>5</v>
@@ -7910,10 +7910,10 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>916</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>917</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>34</v>
@@ -8896,10 +8896,10 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>954</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>955</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>13</v>
@@ -8983,10 +8983,10 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>34</v>
@@ -9708,10 +9708,10 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>940</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>941</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>942</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>10</v>
@@ -9940,10 +9940,10 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>937</v>
-      </c>
-      <c r="B231" s="1" t="s">
-        <v>938</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>34</v>
@@ -10433,10 +10433,10 @@
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="B248" s="1" t="s">
         <v>927</v>
-      </c>
-      <c r="B248" s="1" t="s">
-        <v>928</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>5</v>
@@ -10868,10 +10868,10 @@
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>947</v>
-      </c>
-      <c r="B263" s="1" t="s">
-        <v>948</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>34</v>
@@ -10955,10 +10955,10 @@
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="B266" s="1" t="s">
         <v>931</v>
-      </c>
-      <c r="B266" s="1" t="s">
-        <v>932</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>34</v>
@@ -11651,10 +11651,10 @@
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="B290" s="1" t="s">
         <v>950</v>
-      </c>
-      <c r="B290" s="1" t="s">
-        <v>951</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>34</v>
@@ -11912,10 +11912,10 @@
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="B299" s="1" t="s">
         <v>943</v>
-      </c>
-      <c r="B299" s="1" t="s">
-        <v>944</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>34</v>
@@ -12463,10 +12463,10 @@
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="B318" s="1" t="s">
         <v>935</v>
-      </c>
-      <c r="B318" s="1" t="s">
-        <v>936</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>10</v>
@@ -12782,10 +12782,10 @@
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="B329" s="1" t="s">
         <v>912</v>
-      </c>
-      <c r="B329" s="1" t="s">
-        <v>913</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>10</v>
@@ -13275,10 +13275,10 @@
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="B346" s="1" t="s">
         <v>910</v>
-      </c>
-      <c r="B346" s="1" t="s">
-        <v>911</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>13</v>
@@ -13362,10 +13362,10 @@
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="B349" s="1" t="s">
         <v>933</v>
-      </c>
-      <c r="B349" s="1" t="s">
-        <v>934</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>5</v>
@@ -13913,10 +13913,10 @@
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="B368" s="1" t="s">
         <v>929</v>
-      </c>
-      <c r="B368" s="1" t="s">
-        <v>930</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>97</v>
@@ -14957,10 +14957,10 @@
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="B404" s="1" t="s">
         <v>925</v>
-      </c>
-      <c r="B404" s="1" t="s">
-        <v>926</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>5</v>
@@ -15827,10 +15827,10 @@
     </row>
     <row r="434" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
+        <v>944</v>
+      </c>
+      <c r="B434" t="s">
         <v>945</v>
-      </c>
-      <c r="B434" t="s">
-        <v>946</v>
       </c>
       <c r="C434" t="s">
         <v>10</v>
@@ -15972,10 +15972,10 @@
     </row>
     <row r="439" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
+        <v>922</v>
+      </c>
+      <c r="B439" t="s">
         <v>923</v>
-      </c>
-      <c r="B439" t="s">
-        <v>924</v>
       </c>
       <c r="C439" t="s">
         <v>13</v>
@@ -16320,10 +16320,10 @@
     </row>
     <row r="451" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
+        <v>917</v>
+      </c>
+      <c r="B451" t="s">
         <v>918</v>
-      </c>
-      <c r="B451" t="s">
-        <v>919</v>
       </c>
       <c r="C451" t="s">
         <v>34</v>
@@ -16494,10 +16494,10 @@
     </row>
     <row r="457" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
+        <v>913</v>
+      </c>
+      <c r="B457" t="s">
         <v>914</v>
-      </c>
-      <c r="B457" t="s">
-        <v>915</v>
       </c>
       <c r="C457" t="s">
         <v>5</v>

--- a/excel/clientes_finanzas.xlsx
+++ b/excel/clientes_finanzas.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ferremax-catalogo\excel\"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="962">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="963">
   <si>
     <t>Cliente_ID</t>
   </si>
@@ -2913,12 +2913,15 @@
   </si>
   <si>
     <t>CORRALON NANO</t>
+  </si>
+  <si>
+    <t>FARRETERIA VALVERDE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
@@ -2973,7 +2976,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2993,6 +2996,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17004,7 +17010,33 @@
       </c>
     </row>
     <row r="474" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="I474" s="8"/>
+      <c r="A474" s="9">
+        <v>70118</v>
+      </c>
+      <c r="B474" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="C474" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D474">
+        <v>0</v>
+      </c>
+      <c r="E474">
+        <v>0</v>
+      </c>
+      <c r="F474">
+        <v>0</v>
+      </c>
+      <c r="G474">
+        <v>0</v>
+      </c>
+      <c r="H474">
+        <v>0</v>
+      </c>
+      <c r="I474" s="8">
+        <v>46315</v>
+      </c>
     </row>
     <row r="475" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I475" s="8"/>

--- a/excel/clientes_finanzas.xlsx
+++ b/excel/clientes_finanzas.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$I$470</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$I$474</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="963">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1429" uniqueCount="964">
   <si>
     <t>Cliente_ID</t>
   </si>
@@ -2916,6 +2916,9 @@
   </si>
   <si>
     <t>FARRETERIA VALVERDE</t>
+  </si>
+  <si>
+    <t>FERRETERIA SENEGAL</t>
   </si>
 </sst>
 </file>
@@ -5765,7 +5768,7 @@
         <v>920</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D86" s="7">
         <v>921301.52</v>
@@ -17039,13 +17042,39 @@
       </c>
     </row>
     <row r="475" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="I475" s="8"/>
+      <c r="A475" s="9">
+        <v>20307</v>
+      </c>
+      <c r="B475" t="s">
+        <v>963</v>
+      </c>
+      <c r="C475" t="s">
+        <v>34</v>
+      </c>
+      <c r="D475">
+        <v>0</v>
+      </c>
+      <c r="E475">
+        <v>0</v>
+      </c>
+      <c r="F475">
+        <v>0</v>
+      </c>
+      <c r="G475">
+        <v>0</v>
+      </c>
+      <c r="H475">
+        <v>0</v>
+      </c>
+      <c r="I475" s="8">
+        <v>46316</v>
+      </c>
     </row>
     <row r="476" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I476" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I470"/>
+  <autoFilter ref="A1:I474"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/excel/clientes_finanzas.xlsx
+++ b/excel/clientes_finanzas.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ferremax-catalogo\excel\"/>
@@ -2933,7 +2933,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
@@ -5749,7 +5749,7 @@
         <v>920</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D85" s="7">
         <v>921301.52</v>
